--- a/output/P12.xlsx
+++ b/output/P12.xlsx
@@ -904,15 +904,16 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Assistant</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>Prompt</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr"/>
+      <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Base directory for this skill: /tmp/claude-1000/bundled-skills/2.1.241/892a8c75cc2e65234c070507a8701624/dataviz
 # Data Visualization
@@ -1012,7 +1013,6 @@
 | `scripts/validate_palette.js` | Runnable six-checks validator (run it; don't eyeball) |</t>
         </is>
       </c>
-      <c r="E13" s="1" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
